--- a/output/laminas_provinciales/prov_i_ingr_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:05</t>
+    <t xml:space="preserve">2026-09-09 22:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:01</t>
+    <t xml:space="preserve">2026-09-17 13:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,18 +955,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1086265.88</v>
+        <v>1170958.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1170958.5</v>
+        <v>1086265.88</v>
       </c>
     </row>
     <row r="4">
@@ -1015,68 +1015,68 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>910519.56</v>
+        <v>986483.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1026000.38</v>
+        <v>1104993.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1086265.88</v>
+        <v>1170958.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>986483.75</v>
+        <v>910519.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1104993.88</v>
+        <v>1026000.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1170958.5</v>
+        <v>1086265.88</v>
       </c>
     </row>
     <row r="8">

--- a/output/laminas_provinciales/prov_i_ingr_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:32</t>
+    <t xml:space="preserve">2026-09-25 21:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -665,7 +665,7 @@
         <v>996277.06</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>60667.32</v>
+        <v>60667.31</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>6.09</v>
@@ -688,7 +688,7 @@
         <v>1113669.75</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>71862.37</v>
+        <v>71862.38</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>6.45</v>
@@ -826,7 +826,7 @@
         <v>1168966.75</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>71356.37</v>
+        <v>71356.38</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>6.1</v>

--- a/output/laminas_provinciales/prov_i_ingr_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2024_los_lagos.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:34</t>
+    <t xml:space="preserve">2026-10-05 07:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -500,7 +500,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1170958</v>
+        <v>1170959</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>1104994</v>
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1163806</v>
+        <v>1163807</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1088575</v>
@@ -727,7 +727,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1012468</v>
+        <v>1012469</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>1125779</v>
